--- a/web/files/港岛-西营盘及上环-15 Western Street.xlsx
+++ b/web/files/港岛-西营盘及上环-15 Western Street.xlsx
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>5939000</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>27883</v>
+        <v>28014</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>5939000</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>27883</v>
+        <v>28014</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
@@ -8371,9 +8371,9 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>C | 213呎 (开放式)
+          <t>C | 212呎 (开放式)
 $594万
-$27,883/呎
+$28,014/呎
 (20年-05月-26日)</t>
         </is>
       </c>

--- a/web/files/港岛-西营盘及上环-15 Western Street.xlsx
+++ b/web/files/港岛-西营盘及上环-15 Western Street.xlsx
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>7558000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>35651</v>
+        <v>35484</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>7558000</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>35651</v>
+        <v>35484</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>7558000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>35651</v>
+        <v>35484</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>7558000</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>35651</v>
+        <v>35484</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>11149000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>32695</v>
+        <v>32791</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>11149000</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>32695</v>
+        <v>32791</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>11200000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>36364</v>
+        <v>36482</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>11200000</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>36364</v>
+        <v>36482</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>7198000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>33953</v>
+        <v>33793</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>7198000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>33953</v>
+        <v>33793</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>7198000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>33953</v>
+        <v>33793</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>7198000</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>33953</v>
+        <v>33793</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>10973000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>32179</v>
+        <v>32274</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>10973000</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>32179</v>
+        <v>32274</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>6982000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>32934</v>
+        <v>32779</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>6982000</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>32934</v>
+        <v>32779</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>7029000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>33156</v>
+        <v>33000</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>7029000</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>33156</v>
+        <v>33000</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>10653000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>31240</v>
+        <v>31332</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>10653000</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>31240</v>
+        <v>31332</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>6987000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>32958</v>
+        <v>32803</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>6987000</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>32958</v>
+        <v>32803</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>6987000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>32958</v>
+        <v>32803</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>6987000</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>32958</v>
+        <v>32803</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>6906000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>32575</v>
+        <v>32423</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>6906000</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>32575</v>
+        <v>32423</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>6906000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>32575</v>
+        <v>32423</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>6906000</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>32575</v>
+        <v>32423</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>10443000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>30625</v>
+        <v>30715</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>10443000</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>30625</v>
+        <v>30715</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>10078000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>32721</v>
+        <v>32827</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>10078000</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>32721</v>
+        <v>32827</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>6873000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>32420</v>
+        <v>32268</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>6873000</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>32420</v>
+        <v>32268</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>6095000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>28750</v>
+        <v>28615</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>6095000</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>28750</v>
+        <v>28615</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>10172000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>29830</v>
+        <v>29918</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>10172000</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>29830</v>
+        <v>29918</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>6841000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>32269</v>
+        <v>32117</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>6841000</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>32269</v>
+        <v>32117</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>6841000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>32269</v>
+        <v>32117</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>6841000</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>32269</v>
+        <v>32117</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>9293400</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>30173</v>
+        <v>30272</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         <v>9293400</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>30173</v>
+        <v>30272</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>7490000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>35330</v>
+        <v>35164</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>7490000</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>35330</v>
+        <v>35164</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>6839000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>32259</v>
+        <v>32108</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>6839000</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>32259</v>
+        <v>32108</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>9821000</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>31886</v>
+        <v>31990</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>9821000</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>31886</v>
+        <v>31990</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>9200000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>29870</v>
+        <v>29967</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>9200000</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>29870</v>
+        <v>29967</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>7015000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>33090</v>
+        <v>32934</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>7015000</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>33090</v>
+        <v>32934</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>9649000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>28296</v>
+        <v>28379</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>9649000</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>28296</v>
+        <v>28379</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>6363000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>30014</v>
+        <v>29873</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>6363000</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>30014</v>
+        <v>29873</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>6922000</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>32651</v>
+        <v>32498</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>6922000</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>32651</v>
+        <v>32498</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>6922000</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>32651</v>
+        <v>32498</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>6922000</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>32651</v>
+        <v>32498</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>9970000</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>29238</v>
+        <v>29324</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>9970000</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>29238</v>
+        <v>29324</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>9377000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>30445</v>
+        <v>30544</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>9377000</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>30445</v>
+        <v>30544</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>6278000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>29613</v>
+        <v>29474</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         <v>6278000</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>29613</v>
+        <v>29474</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>9999000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>29323</v>
+        <v>29409</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>9999000</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>29323</v>
+        <v>29409</v>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>9330000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>30292</v>
+        <v>30391</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>9330000</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>30292</v>
+        <v>30391</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>6237000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>29420</v>
+        <v>29282</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5493,7 +5493,7 @@
         <v>6237000</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>29420</v>
+        <v>29282</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>9075000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>29464</v>
+        <v>29560</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>9075000</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>29464</v>
+        <v>29560</v>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>6539000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>30844</v>
+        <v>30700</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>6539000</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>30844</v>
+        <v>30700</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>9999000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>29323</v>
+        <v>29409</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>9999000</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>29323</v>
+        <v>29409</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>6680000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>31509</v>
+        <v>31362</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>6680000</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>31509</v>
+        <v>31362</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>6153000</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>29024</v>
+        <v>28887</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>6153000</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>29024</v>
+        <v>28887</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>9258000</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>27150</v>
+        <v>27229</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>9258000</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>27150</v>
+        <v>27229</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>6331000</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>29863</v>
+        <v>29723</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>6331000</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>29863</v>
+        <v>29723</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>8638000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>28045</v>
+        <v>28137</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>8638000</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>28045</v>
+        <v>28137</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -6722,7 +6722,7 @@
         <v>6361000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>30005</v>
+        <v>29864</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>6361000</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>30005</v>
+        <v>29864</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>6361000</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>30005</v>
+        <v>29864</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>6361000</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>30005</v>
+        <v>29864</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>9131000</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>26777</v>
+        <v>26856</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>9131000</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>26777</v>
+        <v>26856</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>5939000</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>28014</v>
+        <v>27883</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>5939000</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>28014</v>
+        <v>27883</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>9068000</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>26592</v>
+        <v>26671</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>9068000</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>26592</v>
+        <v>26671</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -7509,33 +7509,33 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 308呎 (1房)
+          <t>A | 307呎 (1房)
 $1120万
-$36,364/呎
+$36,482/呎
 (26年-05月-04日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 341呎 (1房)
+          <t>B | 340呎 (1房)
 $1115万
-$32,695/呎
+$32,791/呎
 (22年-04月-21日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>C | 212呎 (开放式)
+          <t>C | 213呎 (开放式)
 $756万
-$35,651/呎
+$35,484/呎
 (24年-03月-27日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $756万
-$35,651/呎
+$35,484/呎
 (24年-03月-27日)</t>
         </is>
       </c>
@@ -7564,25 +7564,25 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 341呎 (1房)
+          <t>B | 340呎 (1房)
 $1097万
-$32,179/呎
+$32,274/呎
 (21年-06月-25日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>C | 212呎 (开放式)
+          <t>C | 213呎 (开放式)
 $720万
-$33,953/呎
+$33,793/呎
 (24年-03月-27日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $720万
-$33,953/呎
+$33,793/呎
 (24年-03月-27日)</t>
         </is>
       </c>
@@ -7611,25 +7611,25 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 341呎 (1房)
+          <t>B | 340呎 (1房)
 $1065万
-$31,240/呎
+$31,332/呎
 (21年-09月-24日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>C | 212呎 (开放式)
+          <t>C | 213呎 (开放式)
 $703万
-$33,156/呎
+$33,000/呎
 (23年-12月-12日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $698万
-$32,934/呎
+$32,779/呎
 (24年-04月-11日)</t>
         </is>
       </c>
@@ -7666,17 +7666,17 @@
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>C | 212呎 (开放式)
+          <t>C | 213呎 (开放式)
 $699万
-$32,958/呎
+$32,803/呎
 (24年-03月-18日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $699万
-$32,958/呎
+$32,803/呎
 (24年-03月-18日)</t>
         </is>
       </c>
@@ -7697,33 +7697,33 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 308呎 (1房)
+          <t>A | 307呎 (1房)
 $1008万
-$32,721/呎
+$32,827/呎
 (22年-09月-27日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 341呎 (1房)
+          <t>B | 340呎 (1房)
 $1044万
-$30,625/呎
+$30,715/呎
 (21年-05月-25日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>C | 212呎 (开放式)
+          <t>C | 213呎 (开放式)
 $691万
-$32,575/呎
+$32,423/呎
 (24年-03月-18日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $691万
-$32,575/呎
+$32,423/呎
 (24年-03月-18日)</t>
         </is>
       </c>
@@ -7752,25 +7752,25 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 341呎 (1房)
+          <t>B | 340呎 (1房)
 $1017万
-$29,830/呎
+$29,918/呎
 (21年-05月-24日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>C | 212呎 (开放式)
+          <t>C | 213呎 (开放式)
 $610万
-$28,750/呎
+$28,615/呎
 (26年-01月-08日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $687万
-$32,420/呎
+$32,268/呎
 (24年-03月-18日)</t>
         </is>
       </c>
@@ -7791,9 +7791,9 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 308呎 (1房)
+          <t>A | 307呎 (1房)
 $929万
-$30,173/呎
+$30,272/呎
 (25年-05月-29日)</t>
         </is>
       </c>
@@ -7807,17 +7807,17 @@
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>C | 212呎 (开放式)
+          <t>C | 213呎 (开放式)
 $684万
-$32,269/呎
+$32,117/呎
 (22年-08月-02日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $684万
-$32,269/呎
+$32,117/呎
 (24年-03月-18日)</t>
         </is>
       </c>
@@ -7838,9 +7838,9 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 308呎 (1房)
+          <t>A | 307呎 (1房)
 $982万
-$31,886/呎
+$31,990/呎
 (21年-12月-23日)</t>
         </is>
       </c>
@@ -7854,17 +7854,17 @@
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>C | 212呎 (开放式)
+          <t>C | 213呎 (开放式)
 $684万
-$32,259/呎
+$32,108/呎
 (23年-10月-05日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $749万
-$35,330/呎
+$35,164/呎
 (20年-06月-19日)</t>
         </is>
       </c>
@@ -7885,9 +7885,9 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>A | 308呎 (1房)
+          <t>A | 307呎 (1房)
 $920万
-$29,870/呎
+$29,967/呎
 (25年-09月-22日)</t>
         </is>
       </c>
@@ -7940,9 +7940,9 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 341呎 (1房)
+          <t>B | 340呎 (1房)
 $965万
-$28,296/呎
+$28,379/呎
 (21年-02月-18日)</t>
         </is>
       </c>
@@ -7956,9 +7956,9 @@
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $702万
-$33,090/呎
+$32,934/呎
 (20年-02月-05日)</t>
         </is>
       </c>
@@ -7995,9 +7995,9 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>C | 212呎 (开放式)
+          <t>C | 213呎 (开放式)
 $636万
-$30,014/呎
+$29,873/呎
 (20年-02月-06日)</t>
         </is>
       </c>
@@ -8026,33 +8026,33 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>A | 308呎 (1房)
+          <t>A | 307呎 (1房)
 $938万
-$30,445/呎
+$30,544/呎
 (22年-08月-01日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 341呎 (1房)
+          <t>B | 340呎 (1房)
 $997万
-$29,238/呎
+$29,324/呎
 (20年-12月-31日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>C | 212呎 (开放式)
+          <t>C | 213呎 (开放式)
 $692万
-$32,651/呎
+$32,498/呎
 (20年-02月-04日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $692万
-$32,651/呎
+$32,498/呎
 (20年-02月-04日)</t>
         </is>
       </c>
@@ -8073,17 +8073,17 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 308呎 (1房)
+          <t>A | 307呎 (1房)
 $933万
-$30,292/呎
+$30,391/呎
 (21年-12月-09日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 341呎 (1房)
+          <t>B | 340呎 (1房)
 $1000万
-$29,323/呎
+$29,409/呎
 (21年-09月-30日)</t>
         </is>
       </c>
@@ -8097,9 +8097,9 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $628万
-$29,613/呎
+$29,474/呎
 (20年-02月-05日)</t>
         </is>
       </c>
@@ -8120,9 +8120,9 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 308呎 (1房)
+          <t>A | 307呎 (1房)
 $908万
-$29,464/呎
+$29,560/呎
 (21年-07月-06日)</t>
         </is>
       </c>
@@ -8144,9 +8144,9 @@
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $624万
-$29,420/呎
+$29,282/呎
 (20年-02月-07日)</t>
         </is>
       </c>
@@ -8175,9 +8175,9 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 341呎 (1房)
+          <t>B | 340呎 (1房)
 $1000万
-$29,323/呎
+$29,409/呎
 (22年-04月-21日)</t>
         </is>
       </c>
@@ -8191,9 +8191,9 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $654万
-$30,844/呎
+$30,700/呎
 (23年-08月-03日)</t>
         </is>
       </c>
@@ -8222,25 +8222,25 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 341呎 (1房)
+          <t>B | 340呎 (1房)
 $926万
-$27,150/呎
+$27,229/呎
 (21年-05月-26日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>C | 212呎 (开放式)
+          <t>C | 213呎 (开放式)
 $615万
-$29,024/呎
+$28,887/呎
 (20年-02月-10日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $668万
-$31,509/呎
+$31,362/呎
 (22年-05月-05日)</t>
         </is>
       </c>
@@ -8261,9 +8261,9 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>A | 308呎 (1房)
+          <t>A | 307呎 (1房)
 $864万
-$28,045/呎
+$28,137/呎
 (21年-08月-27日)</t>
         </is>
       </c>
@@ -8285,9 +8285,9 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $633万
-$29,863/呎
+$29,723/呎
 (20年-02月-05日)</t>
         </is>
       </c>
@@ -8316,25 +8316,25 @@
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 341呎 (1房)
+          <t>B | 340呎 (1房)
 $913万
-$26,777/呎
+$26,856/呎
 (21年-03月-24日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>C | 212呎 (开放式)
+          <t>C | 213呎 (开放式)
 $636万
-$30,005/呎
+$29,864/呎
 (21年-09月-02日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
-          <t>D | 212呎 (开放式)
+          <t>D | 213呎 (开放式)
 $636万
-$30,005/呎
+$29,864/呎
 (21年-06月-15日)</t>
         </is>
       </c>
@@ -8363,17 +8363,17 @@
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>B | 341呎 (1房)
+          <t>B | 340呎 (1房)
 $907万
-$26,592/呎
+$26,671/呎
 (21年-05月-27日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>C | 212呎 (开放式)
+          <t>C | 213呎 (开放式)
 $594万
-$28,014/呎
+$27,883/呎
 (20年-05月-26日)</t>
         </is>
       </c>
